--- a/lookup.xlsx
+++ b/lookup.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2194998_cognizant_com/Documents/Desktop/Final_RES AI PRO_All Done 1/Final_RES AI PRO_All Done/python_automation_utility/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2194998_cognizant_com/Documents/Desktop/AutoOptix_V2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{8DED2FE9-96A2-42D0-9AE4-5080708F5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="14_{8DED2FE9-96A2-42D0-9AE4-5080708F5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A09A53-5C3A-4F49-AF4D-EBC2939F7063}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0A1DFA8F-19F2-4D04-A498-FC5F4A4BC30D}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$676</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3998" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="779">
   <si>
     <t>Subgroup</t>
   </si>
@@ -2334,6 +2334,48 @@
   </si>
   <si>
     <t>non-actionable</t>
+  </si>
+  <si>
+    <t>PagerDuty</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
+    <t>Termination</t>
+  </si>
+  <si>
+    <t>Contingent Worker</t>
+  </si>
+  <si>
+    <t>Onboarding/Offboarding Request</t>
+  </si>
+  <si>
+    <t>Sharepoint</t>
+  </si>
+  <si>
+    <t>Sharepoint Access</t>
+  </si>
+  <si>
+    <t>Ecom Order</t>
+  </si>
+  <si>
+    <t>Splunk Alert</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>L2</t>
   </si>
 </sst>
 </file>
@@ -2409,7 +2451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2425,6 +2467,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2761,15 +2806,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556B986-2304-4B99-95C9-14CF88AE4CEB}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H676"/>
+  <dimension ref="A1:I691"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.08984375" customWidth="1"/>
+    <col min="1" max="1" width="27.1796875" customWidth="1"/>
     <col min="2" max="2" width="32.7265625" customWidth="1"/>
     <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="106.81640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19442,7 +19487,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="7" t="s">
         <v>761</v>
       </c>
@@ -19464,7 +19509,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="7" t="s">
         <v>762</v>
       </c>
@@ -19486,7 +19531,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="7" t="s">
         <v>763</v>
       </c>
@@ -19508,7 +19553,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="7" t="s">
         <v>764</v>
       </c>
@@ -19529,6 +19574,270 @@
         <f t="shared" si="10"/>
         <v>L1.5</v>
       </c>
+    </row>
+    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A677" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C677" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D677" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F677" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G677" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H677" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A678" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C678" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D678" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F678" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G678" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H678" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A679" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B679" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C679" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D679" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F679" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G679" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H679" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A680" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C680" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D680" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F680" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G680" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H680" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A681" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B681" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C681" s="8"/>
+      <c r="D681" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F681" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G681" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H681" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A682" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C682" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="D682" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F682" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G682" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="H682" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A683" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C683" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="D683" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="E683" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="F683" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="G683" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="H683" s="8" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="1"/>
+      <c r="D684" s="1"/>
+      <c r="E684" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F684" s="2"/>
+      <c r="G684" s="2"/>
+    </row>
+    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A685" s="8"/>
+      <c r="B685" s="8"/>
+      <c r="C685" s="8"/>
+      <c r="D685" s="8"/>
+      <c r="E685" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F685" s="8"/>
+      <c r="G685" s="8"/>
+      <c r="H685" s="8"/>
+      <c r="I685" s="8"/>
+    </row>
+    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A686" s="8"/>
+      <c r="B686" s="8"/>
+      <c r="C686" s="8"/>
+      <c r="D686" s="8"/>
+      <c r="E686" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F686" s="8"/>
+      <c r="G686" s="8"/>
+      <c r="H686" s="8"/>
+      <c r="I686" s="8"/>
+    </row>
+    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A687" s="8"/>
+      <c r="B687" s="8"/>
+      <c r="C687" s="8"/>
+      <c r="D687" s="8"/>
+      <c r="E687" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F687" s="8"/>
+      <c r="G687" s="8"/>
+      <c r="H687" s="8"/>
+      <c r="I687" s="8"/>
+    </row>
+    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A688" s="8"/>
+      <c r="B688" s="8"/>
+      <c r="C688" s="8"/>
+      <c r="D688" s="8"/>
+      <c r="E688" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F688" s="8"/>
+      <c r="G688" s="8"/>
+      <c r="H688" s="8"/>
+      <c r="I688" s="8"/>
+    </row>
+    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A689" s="8"/>
+      <c r="B689" s="8"/>
+      <c r="C689" s="8"/>
+      <c r="D689" s="8"/>
+      <c r="E689" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F689" s="8"/>
+      <c r="G689" s="8"/>
+      <c r="H689" s="8"/>
+      <c r="I689" s="8"/>
+    </row>
+    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A690" s="8"/>
+      <c r="B690" s="8"/>
+      <c r="C690" s="8"/>
+      <c r="D690" s="8"/>
+      <c r="E690" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F690" s="8"/>
+      <c r="G690" s="8"/>
+      <c r="H690" s="8"/>
+      <c r="I690" s="8"/>
+    </row>
+    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A691" s="8"/>
+      <c r="B691" s="8"/>
+      <c r="C691" s="8"/>
+      <c r="D691" s="8"/>
+      <c r="E691" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="F691" s="8"/>
+      <c r="G691" s="8"/>
+      <c r="H691" s="8"/>
+      <c r="I691" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H676" xr:uid="{F2B32AB8-7948-4E69-AD33-69BDDAAC2B40}">

--- a/lookup.xlsx
+++ b/lookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2194998_cognizant_com/Documents/Desktop/AutoOptix_V2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kingn\Downloads\AutoOptix-Final-main\AutoOptix-Final-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="14_{8DED2FE9-96A2-42D0-9AE4-5080708F5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A09A53-5C3A-4F49-AF4D-EBC2939F7063}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EF877C-385C-42CD-B8B3-16F2B0DA878C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0A1DFA8F-19F2-4D04-A498-FC5F4A4BC30D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A1DFA8F-19F2-4D04-A498-FC5F4A4BC30D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4049" uniqueCount="778">
   <si>
     <t>Subgroup</t>
   </si>
@@ -2367,9 +2365,6 @@
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>L1</t>
   </si>
   <si>
     <t>N/A</t>
@@ -2807,18 +2802,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556B986-2304-4B99-95C9-14CF88AE4CEB}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I691"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="106.81640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.77734375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2844,7 +2839,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2862,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2892,7 +2887,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -2917,7 +2912,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2942,7 +2937,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -2967,7 +2962,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -2992,7 +2987,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -3017,7 +3012,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -3040,7 +3035,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -3063,7 +3058,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -3088,7 +3083,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -3113,7 +3108,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -3138,7 +3133,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -3163,7 +3158,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -3186,7 +3181,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -3213,7 +3208,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -3236,7 +3231,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -3261,7 +3256,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -3288,7 +3283,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -3315,7 +3310,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -3340,7 +3335,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>42</v>
       </c>
@@ -3365,7 +3360,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
@@ -3390,7 +3385,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>44</v>
       </c>
@@ -3415,7 +3410,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>46</v>
       </c>
@@ -3440,7 +3435,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>47</v>
       </c>
@@ -3465,7 +3460,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -3490,7 +3485,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>49</v>
       </c>
@@ -3515,7 +3510,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>50</v>
       </c>
@@ -3540,7 +3535,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>51</v>
       </c>
@@ -3565,7 +3560,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>52</v>
       </c>
@@ -3590,7 +3585,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>54</v>
       </c>
@@ -3615,7 +3610,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>56</v>
       </c>
@@ -3640,7 +3635,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>57</v>
       </c>
@@ -3665,7 +3660,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>58</v>
       </c>
@@ -3690,7 +3685,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>59</v>
       </c>
@@ -3713,7 +3708,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>60</v>
       </c>
@@ -3738,7 +3733,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>61</v>
       </c>
@@ -3763,7 +3758,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>62</v>
       </c>
@@ -3788,7 +3783,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>63</v>
       </c>
@@ -3813,7 +3808,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>64</v>
       </c>
@@ -3838,7 +3833,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>65</v>
       </c>
@@ -3863,7 +3858,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>66</v>
       </c>
@@ -3888,7 +3883,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>67</v>
       </c>
@@ -3911,7 +3906,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>68</v>
       </c>
@@ -3934,7 +3929,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>69</v>
       </c>
@@ -3957,7 +3952,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>71</v>
       </c>
@@ -3982,7 +3977,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -4007,7 +4002,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -4032,7 +4027,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
@@ -4057,7 +4052,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>76</v>
       </c>
@@ -4082,7 +4077,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>78</v>
       </c>
@@ -4107,7 +4102,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>79</v>
       </c>
@@ -4130,7 +4125,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
@@ -4155,7 +4150,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>82</v>
       </c>
@@ -4180,7 +4175,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>83</v>
       </c>
@@ -4205,7 +4200,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>84</v>
       </c>
@@ -4230,7 +4225,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>86</v>
       </c>
@@ -4255,7 +4250,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>88</v>
       </c>
@@ -4278,7 +4273,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>90</v>
       </c>
@@ -4303,7 +4298,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>92</v>
       </c>
@@ -4328,7 +4323,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>93</v>
       </c>
@@ -4353,7 +4348,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>94</v>
       </c>
@@ -4378,7 +4373,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>95</v>
       </c>
@@ -4401,7 +4396,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>96</v>
       </c>
@@ -4424,7 +4419,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>97</v>
       </c>
@@ -4449,7 +4444,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>98</v>
       </c>
@@ -4474,7 +4469,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>99</v>
       </c>
@@ -4497,7 +4492,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>100</v>
       </c>
@@ -4520,7 +4515,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>102</v>
       </c>
@@ -4545,7 +4540,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>103</v>
       </c>
@@ -4572,7 +4567,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>104</v>
       </c>
@@ -4597,7 +4592,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>106</v>
       </c>
@@ -4622,7 +4617,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>108</v>
       </c>
@@ -4647,7 +4642,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>109</v>
       </c>
@@ -4670,7 +4665,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>110</v>
       </c>
@@ -4695,7 +4690,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>111</v>
       </c>
@@ -4720,7 +4715,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>113</v>
       </c>
@@ -4745,7 +4740,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>114</v>
       </c>
@@ -4770,7 +4765,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>116</v>
       </c>
@@ -4795,7 +4790,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>118</v>
       </c>
@@ -4820,7 +4815,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>119</v>
       </c>
@@ -4845,7 +4840,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>120</v>
       </c>
@@ -4870,7 +4865,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>122</v>
       </c>
@@ -4895,7 +4890,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>123</v>
       </c>
@@ -4918,7 +4913,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>124</v>
       </c>
@@ -4943,7 +4938,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>126</v>
       </c>
@@ -4968,7 +4963,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>127</v>
       </c>
@@ -4993,7 +4988,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>128</v>
       </c>
@@ -5018,7 +5013,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>129</v>
       </c>
@@ -5043,7 +5038,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>130</v>
       </c>
@@ -5068,7 +5063,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>131</v>
       </c>
@@ -5091,7 +5086,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>132</v>
       </c>
@@ -5116,7 +5111,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>133</v>
       </c>
@@ -5141,7 +5136,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>134</v>
       </c>
@@ -5166,7 +5161,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>135</v>
       </c>
@@ -5189,7 +5184,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>137</v>
       </c>
@@ -5214,7 +5209,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>138</v>
       </c>
@@ -5239,7 +5234,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>139</v>
       </c>
@@ -5264,7 +5259,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>140</v>
       </c>
@@ -5289,7 +5284,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>141</v>
       </c>
@@ -5314,7 +5309,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>142</v>
       </c>
@@ -5339,7 +5334,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>143</v>
       </c>
@@ -5364,7 +5359,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>144</v>
       </c>
@@ -5389,7 +5384,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>146</v>
       </c>
@@ -5414,7 +5409,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>147</v>
       </c>
@@ -5439,7 +5434,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>148</v>
       </c>
@@ -5464,7 +5459,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>150</v>
       </c>
@@ -5487,7 +5482,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>151</v>
       </c>
@@ -5512,7 +5507,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>152</v>
       </c>
@@ -5535,7 +5530,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>153</v>
       </c>
@@ -5560,7 +5555,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>154</v>
       </c>
@@ -5585,7 +5580,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>155</v>
       </c>
@@ -5608,7 +5603,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>156</v>
       </c>
@@ -5631,7 +5626,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>157</v>
       </c>
@@ -5654,7 +5649,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>158</v>
       </c>
@@ -5677,7 +5672,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>159</v>
       </c>
@@ -5700,7 +5695,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>160</v>
       </c>
@@ -5725,7 +5720,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>161</v>
       </c>
@@ -5748,7 +5743,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>162</v>
       </c>
@@ -5771,7 +5766,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>163</v>
       </c>
@@ -5796,7 +5791,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>164</v>
       </c>
@@ -5819,7 +5814,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>165</v>
       </c>
@@ -5844,7 +5839,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>166</v>
       </c>
@@ -5869,7 +5864,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>167</v>
       </c>
@@ -5894,7 +5889,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>169</v>
       </c>
@@ -5919,7 +5914,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>170</v>
       </c>
@@ -5944,7 +5939,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>171</v>
       </c>
@@ -5967,7 +5962,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>173</v>
       </c>
@@ -5992,7 +5987,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>174</v>
       </c>
@@ -6017,7 +6012,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>175</v>
       </c>
@@ -6042,7 +6037,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>176</v>
       </c>
@@ -6065,7 +6060,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>177</v>
       </c>
@@ -6090,7 +6085,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>178</v>
       </c>
@@ -6115,7 +6110,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>179</v>
       </c>
@@ -6140,7 +6135,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>180</v>
       </c>
@@ -6165,7 +6160,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>182</v>
       </c>
@@ -6190,7 +6185,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>183</v>
       </c>
@@ -6215,7 +6210,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>184</v>
       </c>
@@ -6240,7 +6235,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>185</v>
       </c>
@@ -6265,7 +6260,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>186</v>
       </c>
@@ -6290,7 +6285,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>187</v>
       </c>
@@ -6315,7 +6310,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>188</v>
       </c>
@@ -6340,7 +6335,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>189</v>
       </c>
@@ -6363,7 +6358,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>190</v>
       </c>
@@ -6388,7 +6383,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>191</v>
       </c>
@@ -6413,7 +6408,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>193</v>
       </c>
@@ -6438,7 +6433,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>194</v>
       </c>
@@ -6463,7 +6458,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>195</v>
       </c>
@@ -6488,7 +6483,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>196</v>
       </c>
@@ -6513,7 +6508,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>115</v>
       </c>
@@ -6538,7 +6533,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>197</v>
       </c>
@@ -6563,7 +6558,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>198</v>
       </c>
@@ -6588,7 +6583,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>199</v>
       </c>
@@ -6613,7 +6608,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>200</v>
       </c>
@@ -6638,7 +6633,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>201</v>
       </c>
@@ -6663,7 +6658,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>203</v>
       </c>
@@ -6688,7 +6683,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>205</v>
       </c>
@@ -6713,7 +6708,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>206</v>
       </c>
@@ -6736,7 +6731,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>207</v>
       </c>
@@ -6761,7 +6756,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>208</v>
       </c>
@@ -6786,7 +6781,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>209</v>
       </c>
@@ -6811,7 +6806,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>210</v>
       </c>
@@ -6836,7 +6831,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>211</v>
       </c>
@@ -6861,7 +6856,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>212</v>
       </c>
@@ -6886,7 +6881,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>214</v>
       </c>
@@ -6909,7 +6904,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>215</v>
       </c>
@@ -6934,7 +6929,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>216</v>
       </c>
@@ -6957,7 +6952,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>217</v>
       </c>
@@ -6982,7 +6977,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>218</v>
       </c>
@@ -7005,7 +7000,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>219</v>
       </c>
@@ -7030,7 +7025,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>220</v>
       </c>
@@ -7053,7 +7048,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>221</v>
       </c>
@@ -7078,7 +7073,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>222</v>
       </c>
@@ -7101,7 +7096,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>223</v>
       </c>
@@ -7126,7 +7121,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>224</v>
       </c>
@@ -7151,7 +7146,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>225</v>
       </c>
@@ -7176,7 +7171,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>226</v>
       </c>
@@ -7201,7 +7196,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>227</v>
       </c>
@@ -7226,7 +7221,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>228</v>
       </c>
@@ -7251,7 +7246,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>229</v>
       </c>
@@ -7276,7 +7271,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>230</v>
       </c>
@@ -7301,7 +7296,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>231</v>
       </c>
@@ -7324,7 +7319,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>232</v>
       </c>
@@ -7347,7 +7342,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>233</v>
       </c>
@@ -7374,7 +7369,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>234</v>
       </c>
@@ -7399,7 +7394,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>235</v>
       </c>
@@ -7422,7 +7417,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>236</v>
       </c>
@@ -7447,7 +7442,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>237</v>
       </c>
@@ -7470,7 +7465,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>238</v>
       </c>
@@ -7493,7 +7488,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>239</v>
       </c>
@@ -7516,7 +7511,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>240</v>
       </c>
@@ -7539,7 +7534,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>241</v>
       </c>
@@ -7562,7 +7557,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>242</v>
       </c>
@@ -7585,7 +7580,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>243</v>
       </c>
@@ -7608,7 +7603,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>244</v>
       </c>
@@ -7633,7 +7628,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>245</v>
       </c>
@@ -7658,7 +7653,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>246</v>
       </c>
@@ -7683,7 +7678,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>247</v>
       </c>
@@ -7708,7 +7703,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>248</v>
       </c>
@@ -7733,7 +7728,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>249</v>
       </c>
@@ -7758,7 +7753,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>250</v>
       </c>
@@ -7783,7 +7778,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>252</v>
       </c>
@@ -7808,7 +7803,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>253</v>
       </c>
@@ -7831,7 +7826,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>255</v>
       </c>
@@ -7854,7 +7849,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>256</v>
       </c>
@@ -7877,7 +7872,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>257</v>
       </c>
@@ -7902,7 +7897,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>259</v>
       </c>
@@ -7927,7 +7922,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>260</v>
       </c>
@@ -7952,7 +7947,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>261</v>
       </c>
@@ -7977,7 +7972,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>262</v>
       </c>
@@ -8002,7 +7997,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>263</v>
       </c>
@@ -8027,7 +8022,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>264</v>
       </c>
@@ -8052,7 +8047,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>265</v>
       </c>
@@ -8077,7 +8072,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>266</v>
       </c>
@@ -8102,7 +8097,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>267</v>
       </c>
@@ -8127,7 +8122,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>268</v>
       </c>
@@ -8152,7 +8147,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>269</v>
       </c>
@@ -8175,7 +8170,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>271</v>
       </c>
@@ -8200,7 +8195,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>272</v>
       </c>
@@ -8223,7 +8218,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>273</v>
       </c>
@@ -8248,7 +8243,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>274</v>
       </c>
@@ -8273,7 +8268,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>275</v>
       </c>
@@ -8298,7 +8293,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>276</v>
       </c>
@@ -8323,7 +8318,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>277</v>
       </c>
@@ -8348,7 +8343,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>278</v>
       </c>
@@ -8373,7 +8368,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>279</v>
       </c>
@@ -8398,7 +8393,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>280</v>
       </c>
@@ -8423,7 +8418,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>281</v>
       </c>
@@ -8448,7 +8443,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>282</v>
       </c>
@@ -8473,7 +8468,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>283</v>
       </c>
@@ -8498,7 +8493,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>284</v>
       </c>
@@ -8523,7 +8518,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>285</v>
       </c>
@@ -8548,7 +8543,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>286</v>
       </c>
@@ -8573,7 +8568,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>287</v>
       </c>
@@ -8598,7 +8593,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>288</v>
       </c>
@@ -8623,7 +8618,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>290</v>
       </c>
@@ -8648,7 +8643,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>291</v>
       </c>
@@ -8671,7 +8666,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>292</v>
       </c>
@@ -8696,7 +8691,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>293</v>
       </c>
@@ -8721,7 +8716,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>294</v>
       </c>
@@ -8746,7 +8741,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>295</v>
       </c>
@@ -8771,7 +8766,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>296</v>
       </c>
@@ -8796,7 +8791,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>297</v>
       </c>
@@ -8821,7 +8816,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>298</v>
       </c>
@@ -8846,7 +8841,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>299</v>
       </c>
@@ -8871,7 +8866,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>300</v>
       </c>
@@ -8896,7 +8891,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>301</v>
       </c>
@@ -8921,7 +8916,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>302</v>
       </c>
@@ -8946,7 +8941,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>303</v>
       </c>
@@ -8971,7 +8966,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>304</v>
       </c>
@@ -8996,7 +8991,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>305</v>
       </c>
@@ -9021,7 +9016,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>306</v>
       </c>
@@ -9046,7 +9041,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>307</v>
       </c>
@@ -9071,7 +9066,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>308</v>
       </c>
@@ -9096,7 +9091,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>309</v>
       </c>
@@ -9121,7 +9116,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>310</v>
       </c>
@@ -9146,7 +9141,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>311</v>
       </c>
@@ -9171,7 +9166,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>312</v>
       </c>
@@ -9196,7 +9191,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>313</v>
       </c>
@@ -9221,7 +9216,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>314</v>
       </c>
@@ -9246,7 +9241,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>315</v>
       </c>
@@ -9271,7 +9266,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>316</v>
       </c>
@@ -9296,7 +9291,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>317</v>
       </c>
@@ -9321,7 +9316,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>318</v>
       </c>
@@ -9346,7 +9341,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>319</v>
       </c>
@@ -9371,7 +9366,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>320</v>
       </c>
@@ -9396,7 +9391,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>321</v>
       </c>
@@ -9421,7 +9416,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>322</v>
       </c>
@@ -9446,7 +9441,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>323</v>
       </c>
@@ -9471,7 +9466,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
         <v>324</v>
       </c>
@@ -9496,7 +9491,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>325</v>
       </c>
@@ -9521,7 +9516,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
         <v>326</v>
       </c>
@@ -9546,7 +9541,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>327</v>
       </c>
@@ -9571,7 +9566,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
         <v>328</v>
       </c>
@@ -9596,7 +9591,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>329</v>
       </c>
@@ -9621,7 +9616,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>330</v>
       </c>
@@ -9646,7 +9641,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
         <v>331</v>
       </c>
@@ -9669,7 +9664,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
         <v>333</v>
       </c>
@@ -9694,7 +9689,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
         <v>335</v>
       </c>
@@ -9719,7 +9714,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
         <v>337</v>
       </c>
@@ -9744,7 +9739,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>338</v>
       </c>
@@ -9767,7 +9762,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>340</v>
       </c>
@@ -9792,7 +9787,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
         <v>341</v>
       </c>
@@ -9817,7 +9812,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
         <v>342</v>
       </c>
@@ -9842,7 +9837,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
         <v>343</v>
       </c>
@@ -9867,7 +9862,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
         <v>344</v>
       </c>
@@ -9892,7 +9887,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
         <v>345</v>
       </c>
@@ -9917,7 +9912,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
         <v>346</v>
       </c>
@@ -9942,7 +9937,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
         <v>347</v>
       </c>
@@ -9967,7 +9962,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
         <v>348</v>
       </c>
@@ -9992,7 +9987,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
         <v>350</v>
       </c>
@@ -10017,7 +10012,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
         <v>351</v>
       </c>
@@ -10042,7 +10037,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
         <v>352</v>
       </c>
@@ -10065,7 +10060,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
         <v>353</v>
       </c>
@@ -10090,7 +10085,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
         <v>354</v>
       </c>
@@ -10115,7 +10110,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
         <v>355</v>
       </c>
@@ -10140,7 +10135,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
         <v>357</v>
       </c>
@@ -10165,7 +10160,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
         <v>359</v>
       </c>
@@ -10190,7 +10185,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
         <v>360</v>
       </c>
@@ -10215,7 +10210,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
         <v>361</v>
       </c>
@@ -10240,7 +10235,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>101</v>
       </c>
@@ -10265,7 +10260,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
         <v>362</v>
       </c>
@@ -10290,7 +10285,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
         <v>364</v>
       </c>
@@ -10315,7 +10310,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
         <v>365</v>
       </c>
@@ -10340,7 +10335,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
         <v>367</v>
       </c>
@@ -10365,7 +10360,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
         <v>368</v>
       </c>
@@ -10390,7 +10385,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
         <v>369</v>
       </c>
@@ -10415,7 +10410,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
         <v>370</v>
       </c>
@@ -10440,7 +10435,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
         <v>55</v>
       </c>
@@ -10465,7 +10460,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
         <v>371</v>
       </c>
@@ -10490,7 +10485,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
         <v>372</v>
       </c>
@@ -10515,7 +10510,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
         <v>373</v>
       </c>
@@ -10540,7 +10535,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
         <v>374</v>
       </c>
@@ -10565,7 +10560,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
         <v>376</v>
       </c>
@@ -10590,7 +10585,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>377</v>
       </c>
@@ -10613,7 +10608,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
         <v>378</v>
       </c>
@@ -10636,7 +10631,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
         <v>379</v>
       </c>
@@ -10661,7 +10656,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
         <v>380</v>
       </c>
@@ -10686,7 +10681,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
         <v>382</v>
       </c>
@@ -10711,7 +10706,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>383</v>
       </c>
@@ -10736,7 +10731,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>384</v>
       </c>
@@ -10761,7 +10756,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
         <v>385</v>
       </c>
@@ -10786,7 +10781,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
         <v>386</v>
       </c>
@@ -10811,7 +10806,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
         <v>387</v>
       </c>
@@ -10836,7 +10831,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>388</v>
       </c>
@@ -10861,7 +10856,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
         <v>389</v>
       </c>
@@ -10886,7 +10881,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>390</v>
       </c>
@@ -10911,7 +10906,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>391</v>
       </c>
@@ -10936,7 +10931,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>392</v>
       </c>
@@ -10961,7 +10956,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>393</v>
       </c>
@@ -10986,7 +10981,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>394</v>
       </c>
@@ -11011,7 +11006,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>395</v>
       </c>
@@ -11036,7 +11031,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
         <v>396</v>
       </c>
@@ -11063,7 +11058,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
         <v>397</v>
       </c>
@@ -11088,7 +11083,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>398</v>
       </c>
@@ -11113,7 +11108,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
         <v>400</v>
       </c>
@@ -11138,7 +11133,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>401</v>
       </c>
@@ -11163,7 +11158,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
         <v>402</v>
       </c>
@@ -11188,7 +11183,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>403</v>
       </c>
@@ -11213,7 +11208,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
         <v>404</v>
       </c>
@@ -11238,7 +11233,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
         <v>405</v>
       </c>
@@ -11263,7 +11258,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>406</v>
       </c>
@@ -11288,7 +11283,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
         <v>407</v>
       </c>
@@ -11313,7 +11308,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>408</v>
       </c>
@@ -11338,7 +11333,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>409</v>
       </c>
@@ -11363,7 +11358,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
         <v>411</v>
       </c>
@@ -11388,7 +11383,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>412</v>
       </c>
@@ -11413,7 +11408,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
         <v>413</v>
       </c>
@@ -11438,7 +11433,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>414</v>
       </c>
@@ -11463,7 +11458,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
         <v>416</v>
       </c>
@@ -11488,7 +11483,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
         <v>417</v>
       </c>
@@ -11513,7 +11508,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>418</v>
       </c>
@@ -11538,7 +11533,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>419</v>
       </c>
@@ -11561,7 +11556,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
         <v>420</v>
       </c>
@@ -11586,7 +11581,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>421</v>
       </c>
@@ -11609,7 +11604,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
         <v>422</v>
       </c>
@@ -11634,7 +11629,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
         <v>423</v>
       </c>
@@ -11659,7 +11654,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>425</v>
       </c>
@@ -11684,7 +11679,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
         <v>426</v>
       </c>
@@ -11709,7 +11704,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>427</v>
       </c>
@@ -11734,7 +11729,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>428</v>
       </c>
@@ -11759,7 +11754,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
         <v>430</v>
       </c>
@@ -11784,7 +11779,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>432</v>
       </c>
@@ -11807,7 +11802,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
         <v>433</v>
       </c>
@@ -11832,7 +11827,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>434</v>
       </c>
@@ -11857,7 +11852,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>435</v>
       </c>
@@ -11882,7 +11877,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>436</v>
       </c>
@@ -11907,7 +11902,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>437</v>
       </c>
@@ -11932,7 +11927,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
         <v>438</v>
       </c>
@@ -11957,7 +11952,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
         <v>440</v>
       </c>
@@ -11982,7 +11977,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
         <v>441</v>
       </c>
@@ -12007,7 +12002,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>443</v>
       </c>
@@ -12032,7 +12027,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>444</v>
       </c>
@@ -12057,7 +12052,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
         <v>445</v>
       </c>
@@ -12082,7 +12077,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>446</v>
       </c>
@@ -12107,7 +12102,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
         <v>447</v>
       </c>
@@ -12132,7 +12127,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>448</v>
       </c>
@@ -12157,7 +12152,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
         <v>449</v>
       </c>
@@ -12182,7 +12177,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
         <v>450</v>
       </c>
@@ -12205,7 +12200,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
         <v>451</v>
       </c>
@@ -12230,7 +12225,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>452</v>
       </c>
@@ -12255,7 +12250,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
         <v>453</v>
       </c>
@@ -12280,7 +12275,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
         <v>454</v>
       </c>
@@ -12305,7 +12300,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>455</v>
       </c>
@@ -12330,7 +12325,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
         <v>456</v>
       </c>
@@ -12355,7 +12350,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
         <v>457</v>
       </c>
@@ -12380,7 +12375,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>458</v>
       </c>
@@ -12405,7 +12400,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
         <v>459</v>
       </c>
@@ -12430,7 +12425,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
         <v>460</v>
       </c>
@@ -12457,7 +12452,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
         <v>461</v>
       </c>
@@ -12484,7 +12479,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
         <v>462</v>
       </c>
@@ -12509,7 +12504,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
         <v>463</v>
       </c>
@@ -12536,7 +12531,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
         <v>464</v>
       </c>
@@ -12563,7 +12558,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
         <v>465</v>
       </c>
@@ -12586,7 +12581,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
         <v>466</v>
       </c>
@@ -12609,7 +12604,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
         <v>467</v>
       </c>
@@ -12632,7 +12627,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
         <v>468</v>
       </c>
@@ -12659,7 +12654,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
         <v>470</v>
       </c>
@@ -12684,7 +12679,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>471</v>
       </c>
@@ -12709,7 +12704,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>472</v>
       </c>
@@ -12734,7 +12729,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
         <v>474</v>
       </c>
@@ -12759,7 +12754,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
         <v>475</v>
       </c>
@@ -12782,7 +12777,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
         <v>476</v>
       </c>
@@ -12807,7 +12802,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
         <v>478</v>
       </c>
@@ -12832,7 +12827,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>479</v>
       </c>
@@ -12857,7 +12852,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
         <v>480</v>
       </c>
@@ -12882,7 +12877,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
         <v>481</v>
       </c>
@@ -12907,7 +12902,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
         <v>482</v>
       </c>
@@ -12932,7 +12927,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
         <v>483</v>
       </c>
@@ -12957,7 +12952,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
         <v>484</v>
       </c>
@@ -12982,7 +12977,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
         <v>485</v>
       </c>
@@ -13005,7 +13000,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
         <v>486</v>
       </c>
@@ -13030,7 +13025,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
         <v>487</v>
       </c>
@@ -13055,7 +13050,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
         <v>488</v>
       </c>
@@ -13080,7 +13075,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
         <v>490</v>
       </c>
@@ -13107,7 +13102,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
         <v>491</v>
       </c>
@@ -13132,7 +13127,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
         <v>492</v>
       </c>
@@ -13157,7 +13152,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
         <v>493</v>
       </c>
@@ -13182,7 +13177,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
         <v>495</v>
       </c>
@@ -13207,7 +13202,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
         <v>496</v>
       </c>
@@ -13232,7 +13227,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
         <v>497</v>
       </c>
@@ -13257,7 +13252,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
         <v>498</v>
       </c>
@@ -13282,7 +13277,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
         <v>500</v>
       </c>
@@ -13307,7 +13302,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
         <v>501</v>
       </c>
@@ -13332,7 +13327,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
         <v>502</v>
       </c>
@@ -13357,7 +13352,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
         <v>503</v>
       </c>
@@ -13382,7 +13377,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
         <v>504</v>
       </c>
@@ -13409,7 +13404,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
         <v>505</v>
       </c>
@@ -13434,7 +13429,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
         <v>506</v>
       </c>
@@ -13459,7 +13454,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
         <v>508</v>
       </c>
@@ -13484,7 +13479,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
         <v>509</v>
       </c>
@@ -13509,7 +13504,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
         <v>510</v>
       </c>
@@ -13534,7 +13529,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
         <v>511</v>
       </c>
@@ -13559,7 +13554,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
         <v>512</v>
       </c>
@@ -13584,7 +13579,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
         <v>514</v>
       </c>
@@ -13609,7 +13604,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
         <v>515</v>
       </c>
@@ -13634,7 +13629,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
         <v>516</v>
       </c>
@@ -13659,7 +13654,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
         <v>517</v>
       </c>
@@ -13684,7 +13679,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
         <v>519</v>
       </c>
@@ -13709,7 +13704,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
         <v>520</v>
       </c>
@@ -13734,7 +13729,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
         <v>521</v>
       </c>
@@ -13759,7 +13754,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
         <v>522</v>
       </c>
@@ -13784,7 +13779,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
         <v>523</v>
       </c>
@@ -13807,7 +13802,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
         <v>524</v>
       </c>
@@ -13832,7 +13827,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
         <v>525</v>
       </c>
@@ -13857,7 +13852,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>526</v>
       </c>
@@ -13882,7 +13877,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>527</v>
       </c>
@@ -13907,7 +13902,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>528</v>
       </c>
@@ -13932,7 +13927,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>529</v>
       </c>
@@ -13957,7 +13952,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>530</v>
       </c>
@@ -13982,7 +13977,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>531</v>
       </c>
@@ -14007,7 +14002,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>532</v>
       </c>
@@ -14034,7 +14029,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>533</v>
       </c>
@@ -14059,7 +14054,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>534</v>
       </c>
@@ -14084,7 +14079,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>535</v>
       </c>
@@ -14109,7 +14104,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>536</v>
       </c>
@@ -14134,7 +14129,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>538</v>
       </c>
@@ -14159,7 +14154,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>539</v>
       </c>
@@ -14184,7 +14179,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>540</v>
       </c>
@@ -14209,7 +14204,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>541</v>
       </c>
@@ -14234,7 +14229,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>542</v>
       </c>
@@ -14259,7 +14254,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>543</v>
       </c>
@@ -14284,7 +14279,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>544</v>
       </c>
@@ -14309,7 +14304,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>545</v>
       </c>
@@ -14334,7 +14329,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>546</v>
       </c>
@@ -14359,7 +14354,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>547</v>
       </c>
@@ -14384,7 +14379,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>548</v>
       </c>
@@ -14409,7 +14404,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>549</v>
       </c>
@@ -14434,7 +14429,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>550</v>
       </c>
@@ -14459,7 +14454,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>551</v>
       </c>
@@ -14484,7 +14479,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>552</v>
       </c>
@@ -14509,7 +14504,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>553</v>
       </c>
@@ -14534,7 +14529,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>554</v>
       </c>
@@ -14559,7 +14554,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>555</v>
       </c>
@@ -14584,7 +14579,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>556</v>
       </c>
@@ -14609,7 +14604,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>557</v>
       </c>
@@ -14634,7 +14629,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>558</v>
       </c>
@@ -14659,7 +14654,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>559</v>
       </c>
@@ -14684,7 +14679,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>560</v>
       </c>
@@ -14709,7 +14704,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>561</v>
       </c>
@@ -14734,7 +14729,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>562</v>
       </c>
@@ -14759,7 +14754,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>563</v>
       </c>
@@ -14784,7 +14779,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>564</v>
       </c>
@@ -14809,7 +14804,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>565</v>
       </c>
@@ -14834,7 +14829,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3" t="s">
         <v>566</v>
       </c>
@@ -14859,7 +14854,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
         <v>567</v>
       </c>
@@ -14884,7 +14879,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3" t="s">
         <v>568</v>
       </c>
@@ -14909,7 +14904,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
         <v>569</v>
       </c>
@@ -14934,7 +14929,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3" t="s">
         <v>570</v>
       </c>
@@ -14959,7 +14954,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
         <v>571</v>
       </c>
@@ -14984,7 +14979,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
         <v>572</v>
       </c>
@@ -15009,7 +15004,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
         <v>573</v>
       </c>
@@ -15034,7 +15029,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3" t="s">
         <v>574</v>
       </c>
@@ -15059,7 +15054,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
         <v>575</v>
       </c>
@@ -15084,7 +15079,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
         <v>576</v>
       </c>
@@ -15109,7 +15104,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
         <v>577</v>
       </c>
@@ -15134,7 +15129,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3" t="s">
         <v>578</v>
       </c>
@@ -15159,7 +15154,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
         <v>579</v>
       </c>
@@ -15184,7 +15179,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3" t="s">
         <v>580</v>
       </c>
@@ -15209,7 +15204,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
         <v>581</v>
       </c>
@@ -15234,7 +15229,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3" t="s">
         <v>582</v>
       </c>
@@ -15259,7 +15254,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
         <v>583</v>
       </c>
@@ -15284,7 +15279,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3" t="s">
         <v>584</v>
       </c>
@@ -15309,7 +15304,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
         <v>585</v>
       </c>
@@ -15334,7 +15329,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
         <v>586</v>
       </c>
@@ -15359,7 +15354,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
         <v>587</v>
       </c>
@@ -15384,7 +15379,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3" t="s">
         <v>588</v>
       </c>
@@ -15409,7 +15404,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
         <v>589</v>
       </c>
@@ -15434,7 +15429,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3" t="s">
         <v>590</v>
       </c>
@@ -15459,7 +15454,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
         <v>591</v>
       </c>
@@ -15484,7 +15479,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3" t="s">
         <v>592</v>
       </c>
@@ -15509,7 +15504,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
         <v>593</v>
       </c>
@@ -15534,7 +15529,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
         <v>594</v>
       </c>
@@ -15559,7 +15554,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
         <v>595</v>
       </c>
@@ -15584,7 +15579,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
         <v>596</v>
       </c>
@@ -15609,7 +15604,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
         <v>597</v>
       </c>
@@ -15634,7 +15629,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3" t="s">
         <v>598</v>
       </c>
@@ -15659,7 +15654,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
         <v>599</v>
       </c>
@@ -15684,7 +15679,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3" t="s">
         <v>600</v>
       </c>
@@ -15709,7 +15704,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
         <v>601</v>
       </c>
@@ -15734,7 +15729,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3" t="s">
         <v>602</v>
       </c>
@@ -15759,7 +15754,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
         <v>603</v>
       </c>
@@ -15784,7 +15779,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
         <v>604</v>
       </c>
@@ -15809,7 +15804,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
         <v>605</v>
       </c>
@@ -15834,7 +15829,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3" t="s">
         <v>606</v>
       </c>
@@ -15859,7 +15854,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
         <v>607</v>
       </c>
@@ -15884,7 +15879,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
         <v>608</v>
       </c>
@@ -15909,7 +15904,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
         <v>609</v>
       </c>
@@ -15934,7 +15929,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
         <v>610</v>
       </c>
@@ -15959,7 +15954,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
         <v>611</v>
       </c>
@@ -15984,7 +15979,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
         <v>612</v>
       </c>
@@ -16009,7 +16004,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
         <v>613</v>
       </c>
@@ -16032,7 +16027,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3" t="s">
         <v>614</v>
       </c>
@@ -16057,7 +16052,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
         <v>615</v>
       </c>
@@ -16082,7 +16077,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A536" s="3" t="s">
         <v>616</v>
       </c>
@@ -16107,7 +16102,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
         <v>617</v>
       </c>
@@ -16130,7 +16125,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="3" t="s">
         <v>618</v>
       </c>
@@ -16155,7 +16150,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
         <v>619</v>
       </c>
@@ -16180,7 +16175,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A540" s="3" t="s">
         <v>620</v>
       </c>
@@ -16205,7 +16200,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
         <v>621</v>
       </c>
@@ -16230,7 +16225,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
         <v>622</v>
       </c>
@@ -16255,7 +16250,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
         <v>624</v>
       </c>
@@ -16280,7 +16275,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
         <v>625</v>
       </c>
@@ -16305,7 +16300,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
         <v>626</v>
       </c>
@@ -16330,7 +16325,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
         <v>627</v>
       </c>
@@ -16355,7 +16350,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
         <v>628</v>
       </c>
@@ -16380,7 +16375,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
         <v>629</v>
       </c>
@@ -16405,7 +16400,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
         <v>630</v>
       </c>
@@ -16430,7 +16425,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
         <v>631</v>
       </c>
@@ -16455,7 +16450,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
         <v>632</v>
       </c>
@@ -16480,7 +16475,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
         <v>633</v>
       </c>
@@ -16505,7 +16500,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
         <v>634</v>
       </c>
@@ -16530,7 +16525,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
         <v>636</v>
       </c>
@@ -16553,7 +16548,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
         <v>638</v>
       </c>
@@ -16578,7 +16573,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
         <v>639</v>
       </c>
@@ -16603,7 +16598,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
         <v>640</v>
       </c>
@@ -16628,7 +16623,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
         <v>641</v>
       </c>
@@ -16653,7 +16648,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
         <v>642</v>
       </c>
@@ -16678,7 +16673,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
         <v>643</v>
       </c>
@@ -16701,7 +16696,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
         <v>644</v>
       </c>
@@ -16726,7 +16721,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
         <v>645</v>
       </c>
@@ -16751,7 +16746,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
         <v>646</v>
       </c>
@@ -16776,7 +16771,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
         <v>647</v>
       </c>
@@ -16801,7 +16796,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
         <v>648</v>
       </c>
@@ -16826,7 +16821,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
         <v>649</v>
       </c>
@@ -16851,7 +16846,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
         <v>650</v>
       </c>
@@ -16876,7 +16871,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
         <v>651</v>
       </c>
@@ -16901,7 +16896,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
         <v>652</v>
       </c>
@@ -16926,7 +16921,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
         <v>653</v>
       </c>
@@ -16951,7 +16946,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
         <v>654</v>
       </c>
@@ -16976,7 +16971,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
         <v>655</v>
       </c>
@@ -17001,7 +16996,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
         <v>656</v>
       </c>
@@ -17026,7 +17021,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
         <v>658</v>
       </c>
@@ -17051,7 +17046,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
         <v>659</v>
       </c>
@@ -17076,7 +17071,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
         <v>661</v>
       </c>
@@ -17101,7 +17096,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
         <v>662</v>
       </c>
@@ -17126,7 +17121,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
         <v>663</v>
       </c>
@@ -17149,7 +17144,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
         <v>664</v>
       </c>
@@ -17174,7 +17169,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
         <v>665</v>
       </c>
@@ -17201,7 +17196,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
         <v>666</v>
       </c>
@@ -17226,7 +17221,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
         <v>667</v>
       </c>
@@ -17251,7 +17246,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
         <v>668</v>
       </c>
@@ -17276,7 +17271,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
         <v>669</v>
       </c>
@@ -17301,7 +17296,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
         <v>670</v>
       </c>
@@ -17326,7 +17321,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
         <v>671</v>
       </c>
@@ -17351,7 +17346,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
         <v>672</v>
       </c>
@@ -17376,7 +17371,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
         <v>673</v>
       </c>
@@ -17401,7 +17396,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
         <v>674</v>
       </c>
@@ -17426,7 +17421,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
         <v>675</v>
       </c>
@@ -17451,7 +17446,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
         <v>676</v>
       </c>
@@ -17476,7 +17471,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
         <v>677</v>
       </c>
@@ -17503,7 +17498,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
         <v>678</v>
       </c>
@@ -17530,7 +17525,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
         <v>679</v>
       </c>
@@ -17557,7 +17552,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
         <v>680</v>
       </c>
@@ -17582,7 +17577,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
         <v>681</v>
       </c>
@@ -17609,7 +17604,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
         <v>682</v>
       </c>
@@ -17636,7 +17631,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="3" t="s">
         <v>683</v>
       </c>
@@ -17661,7 +17656,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
         <v>684</v>
       </c>
@@ -17686,7 +17681,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A600" s="3" t="s">
         <v>685</v>
       </c>
@@ -17711,7 +17706,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
         <v>686</v>
       </c>
@@ -17736,7 +17731,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="3" t="s">
         <v>687</v>
       </c>
@@ -17761,7 +17756,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
         <v>688</v>
       </c>
@@ -17786,7 +17781,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="3" t="s">
         <v>689</v>
       </c>
@@ -17809,7 +17804,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
         <v>690</v>
       </c>
@@ -17834,7 +17829,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A606" s="3" t="s">
         <v>691</v>
       </c>
@@ -17859,7 +17854,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
         <v>692</v>
       </c>
@@ -17886,7 +17881,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="3" t="s">
         <v>693</v>
       </c>
@@ -17911,7 +17906,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
         <v>694</v>
       </c>
@@ -17934,7 +17929,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
         <v>695</v>
       </c>
@@ -17961,7 +17956,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
         <v>696</v>
       </c>
@@ -17986,7 +17981,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A612" s="3" t="s">
         <v>697</v>
       </c>
@@ -18013,7 +18008,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
         <v>698</v>
       </c>
@@ -18040,7 +18035,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A614" s="3" t="s">
         <v>699</v>
       </c>
@@ -18067,7 +18062,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
         <v>700</v>
       </c>
@@ -18094,7 +18089,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A616" s="3" t="s">
         <v>701</v>
       </c>
@@ -18121,7 +18116,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
         <v>702</v>
       </c>
@@ -18148,7 +18143,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A618" s="3" t="s">
         <v>703</v>
       </c>
@@ -18175,7 +18170,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
         <v>704</v>
       </c>
@@ -18200,7 +18195,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="3" t="s">
         <v>705</v>
       </c>
@@ -18225,7 +18220,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
         <v>706</v>
       </c>
@@ -18250,7 +18245,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A622" s="3" t="s">
         <v>707</v>
       </c>
@@ -18275,7 +18270,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
         <v>709</v>
       </c>
@@ -18300,7 +18295,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="3" t="s">
         <v>710</v>
       </c>
@@ -18325,7 +18320,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
         <v>711</v>
       </c>
@@ -18350,7 +18345,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
         <v>712</v>
       </c>
@@ -18375,7 +18370,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
         <v>713</v>
       </c>
@@ -18400,7 +18395,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
         <v>714</v>
       </c>
@@ -18425,7 +18420,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
         <v>715</v>
       </c>
@@ -18450,7 +18445,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
         <v>716</v>
       </c>
@@ -18475,7 +18470,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
         <v>717</v>
       </c>
@@ -18500,7 +18495,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A632" s="3" t="s">
         <v>718</v>
       </c>
@@ -18525,7 +18520,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
         <v>719</v>
       </c>
@@ -18550,7 +18545,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
         <v>720</v>
       </c>
@@ -18575,7 +18570,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
         <v>721</v>
       </c>
@@ -18598,7 +18593,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A636" s="3" t="s">
         <v>722</v>
       </c>
@@ -18623,7 +18618,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
         <v>723</v>
       </c>
@@ -18648,7 +18643,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A638" s="3" t="s">
         <v>724</v>
       </c>
@@ -18673,7 +18668,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
         <v>725</v>
       </c>
@@ -18698,7 +18693,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
         <v>726</v>
       </c>
@@ -18723,7 +18718,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
         <v>727</v>
       </c>
@@ -18748,7 +18743,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
         <v>728</v>
       </c>
@@ -18773,7 +18768,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
         <v>729</v>
       </c>
@@ -18796,11 +18791,11 @@
         <v>10</v>
       </c>
       <c r="H643" t="str">
-        <f t="shared" ref="H643:H676" si="10">IF(F643="Feasible", "L1.5", "L2")</f>
-        <v>L1.5</v>
-      </c>
-    </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="H643:H682" si="10">IF(F643="Feasible", "L1.5", "L2")</f>
+        <v>L1.5</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
         <v>730</v>
       </c>
@@ -18827,7 +18822,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
         <v>731</v>
       </c>
@@ -18852,7 +18847,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
         <v>732</v>
       </c>
@@ -18879,7 +18874,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
         <v>733</v>
       </c>
@@ -18904,7 +18899,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
         <v>734</v>
       </c>
@@ -18929,7 +18924,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
         <v>735</v>
       </c>
@@ -18954,7 +18949,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
         <v>736</v>
       </c>
@@ -18979,7 +18974,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
         <v>738</v>
       </c>
@@ -19004,7 +18999,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
         <v>739</v>
       </c>
@@ -19029,7 +19024,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
         <v>740</v>
       </c>
@@ -19054,7 +19049,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
         <v>741</v>
       </c>
@@ -19081,7 +19076,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
         <v>742</v>
       </c>
@@ -19106,7 +19101,7 @@
         <v>L2</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
         <v>743</v>
       </c>
@@ -19131,7 +19126,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
         <v>744</v>
       </c>
@@ -19156,7 +19151,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
         <v>745</v>
       </c>
@@ -19183,7 +19178,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
         <v>746</v>
       </c>
@@ -19208,7 +19203,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="5" t="s">
         <v>747</v>
       </c>
@@ -19229,7 +19224,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="5" t="s">
         <v>749</v>
       </c>
@@ -19250,7 +19245,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="5" t="s">
         <v>750</v>
       </c>
@@ -19271,7 +19266,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="5" t="s">
         <v>751</v>
       </c>
@@ -19292,7 +19287,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="5" t="s">
         <v>752</v>
       </c>
@@ -19313,7 +19308,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="5" t="s">
         <v>753</v>
       </c>
@@ -19334,7 +19329,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="5" t="s">
         <v>754</v>
       </c>
@@ -19355,7 +19350,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="7" t="s">
         <v>755</v>
       </c>
@@ -19377,7 +19372,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="7" t="s">
         <v>756</v>
       </c>
@@ -19399,7 +19394,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="7" t="s">
         <v>757</v>
       </c>
@@ -19421,7 +19416,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="7" t="s">
         <v>758</v>
       </c>
@@ -19443,7 +19438,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="7" t="s">
         <v>759</v>
       </c>
@@ -19465,7 +19460,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="7" t="s">
         <v>760</v>
       </c>
@@ -19487,7 +19482,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="7" t="s">
         <v>761</v>
       </c>
@@ -19509,7 +19504,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="7" t="s">
         <v>762</v>
       </c>
@@ -19531,7 +19526,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="7" t="s">
         <v>763</v>
       </c>
@@ -19553,7 +19548,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="7" t="s">
         <v>764</v>
       </c>
@@ -19575,7 +19570,7 @@
         <v>L1.5</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
         <v>765</v>
       </c>
@@ -19594,11 +19589,12 @@
       <c r="G677" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H677" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H677" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A678" s="3" t="s">
         <v>766</v>
       </c>
@@ -19617,11 +19613,12 @@
       <c r="G678" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H678" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H678" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
         <v>767</v>
       </c>
@@ -19640,11 +19637,12 @@
       <c r="G679" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H679" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H679" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A680" s="3" t="s">
         <v>768</v>
       </c>
@@ -19663,11 +19661,12 @@
       <c r="G680" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H680" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H680" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A681" s="3" t="s">
         <v>770</v>
       </c>
@@ -19684,11 +19683,12 @@
       <c r="G681" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H681" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H681" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A682" s="3" t="s">
         <v>773</v>
       </c>
@@ -19707,11 +19707,12 @@
       <c r="G682" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="H682" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H682" t="str">
+        <f t="shared" si="10"/>
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A683" s="3" t="s">
         <v>772</v>
       </c>
@@ -19719,25 +19720,25 @@
         <v>31</v>
       </c>
       <c r="C683" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="D683" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="E683" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="F683" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="G683" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="H683" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="D683" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="E683" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="F683" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="G683" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="H683" s="8" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -19748,7 +19749,7 @@
       <c r="F684" s="2"/>
       <c r="G684" s="2"/>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A685" s="8"/>
       <c r="B685" s="8"/>
       <c r="C685" s="8"/>
@@ -19761,7 +19762,7 @@
       <c r="H685" s="8"/>
       <c r="I685" s="8"/>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A686" s="8"/>
       <c r="B686" s="8"/>
       <c r="C686" s="8"/>
@@ -19774,7 +19775,7 @@
       <c r="H686" s="8"/>
       <c r="I686" s="8"/>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A687" s="8"/>
       <c r="B687" s="8"/>
       <c r="C687" s="8"/>
@@ -19787,7 +19788,7 @@
       <c r="H687" s="8"/>
       <c r="I687" s="8"/>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A688" s="8"/>
       <c r="B688" s="8"/>
       <c r="C688" s="8"/>
@@ -19800,7 +19801,7 @@
       <c r="H688" s="8"/>
       <c r="I688" s="8"/>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A689" s="8"/>
       <c r="B689" s="8"/>
       <c r="C689" s="8"/>
@@ -19813,7 +19814,7 @@
       <c r="H689" s="8"/>
       <c r="I689" s="8"/>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A690" s="8"/>
       <c r="B690" s="8"/>
       <c r="C690" s="8"/>
@@ -19826,13 +19827,13 @@
       <c r="H690" s="8"/>
       <c r="I690" s="8"/>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A691" s="8"/>
       <c r="B691" s="8"/>
       <c r="C691" s="8"/>
       <c r="D691" s="8"/>
       <c r="E691" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F691" s="8"/>
       <c r="G691" s="8"/>
